--- a/artfynd/Vitstensberget V artfynd.xlsx
+++ b/artfynd/Vitstensberget V artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56606364</v>
       </c>
       <c r="B2" t="n">
-        <v>79012</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>56606363</v>
       </c>
       <c r="B3" t="n">
-        <v>78647</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
